--- a/0_Documents/Kalkulation/Komponentenliste.xlsx
+++ b/0_Documents/Kalkulation/Komponentenliste.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DEV\Lumify\0_Documents\Kalkulation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1E02C322-3BCC-40F4-8414-EC7FEAFEB6E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5CDAE24-4C55-4C6F-A517-38D337DA45D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{42DB02A7-F323-4E09-A6DB-68C0AF5073E0}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="37">
   <si>
     <t>Bezeichnung</t>
   </si>
@@ -147,6 +147,9 @@
   </si>
   <si>
     <t>Gesamtsumme (Netto)</t>
+  </si>
+  <si>
+    <t>S</t>
   </si>
 </sst>
 </file>
@@ -154,7 +157,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="168" formatCode="#,##0.00\ [$€-1];[Red]\-#,##0.00\ [$€-1]"/>
+    <numFmt numFmtId="164" formatCode="#,##0.00\ [$€-1];[Red]\-#,##0.00\ [$€-1]"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -326,19 +329,7 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="2" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -347,23 +338,35 @@
     <xf numFmtId="14" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="14" fontId="3" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="168" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="3" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -699,13 +702,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F26A550-04E7-41E1-A0A9-E176EF97C205}">
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26.42578125" customWidth="1"/>
     <col min="2" max="2" width="22.140625" customWidth="1"/>
-    <col min="3" max="3" width="10.140625" style="16" customWidth="1"/>
-    <col min="4" max="4" width="18.140625" style="16" customWidth="1"/>
+    <col min="3" max="3" width="10.140625" style="10" customWidth="1"/>
+    <col min="4" max="4" width="18.140625" style="10" customWidth="1"/>
     <col min="5" max="5" width="23.85546875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -716,10 +719,10 @@
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="8" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="2" t="s">
@@ -733,10 +736,10 @@
       <c r="B2" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="17">
+      <c r="C2" s="11">
         <v>0</v>
       </c>
-      <c r="D2" s="13">
+      <c r="D2" s="9">
         <v>46149</v>
       </c>
       <c r="E2" s="4" t="s">
@@ -750,10 +753,10 @@
       <c r="B3" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="17">
+      <c r="C3" s="11">
         <v>0</v>
       </c>
-      <c r="D3" s="13">
+      <c r="D3" s="9">
         <v>46149</v>
       </c>
       <c r="E3" s="4" t="s">
@@ -767,10 +770,10 @@
       <c r="B4" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="17">
+      <c r="C4" s="11">
         <v>0</v>
       </c>
-      <c r="D4" s="13">
+      <c r="D4" s="9">
         <v>46149</v>
       </c>
       <c r="E4" s="4" t="s">
@@ -784,10 +787,10 @@
       <c r="B5" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="17">
+      <c r="C5" s="11">
         <v>0</v>
       </c>
-      <c r="D5" s="13">
+      <c r="D5" s="9">
         <v>46149</v>
       </c>
       <c r="E5" s="4" t="s">
@@ -801,10 +804,10 @@
       <c r="B6" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="17">
+      <c r="C6" s="11">
         <v>0</v>
       </c>
-      <c r="D6" s="13">
+      <c r="D6" s="9">
         <v>46160</v>
       </c>
       <c r="E6" s="4" t="s">
@@ -818,10 +821,10 @@
       <c r="B7" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="C7" s="17">
+      <c r="C7" s="11">
         <v>0</v>
       </c>
-      <c r="D7" s="13">
+      <c r="D7" s="9">
         <v>46149</v>
       </c>
       <c r="E7" s="4" t="s">
@@ -835,10 +838,10 @@
       <c r="B8" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C8" s="17">
+      <c r="C8" s="11">
         <v>0</v>
       </c>
-      <c r="D8" s="13">
+      <c r="D8" s="9">
         <v>46149</v>
       </c>
       <c r="E8" s="4" t="s">
@@ -852,10 +855,10 @@
       <c r="B9" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="C9" s="17">
+      <c r="C9" s="11">
         <v>0</v>
       </c>
-      <c r="D9" s="13">
+      <c r="D9" s="9">
         <v>46149</v>
       </c>
       <c r="E9" s="4" t="s">
@@ -869,10 +872,10 @@
       <c r="B10" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="C10" s="17">
+      <c r="C10" s="11">
         <v>0</v>
       </c>
-      <c r="D10" s="13">
+      <c r="D10" s="9">
         <v>46195</v>
       </c>
       <c r="E10" s="4" t="s">
@@ -883,16 +886,16 @@
       <c r="A11" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="B11" s="8" t="s">
+      <c r="B11" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="C11" s="18">
+      <c r="C11" s="14">
         <v>6</v>
       </c>
-      <c r="D11" s="14">
+      <c r="D11" s="16">
         <v>46195</v>
       </c>
-      <c r="E11" s="8" t="s">
+      <c r="E11" s="12" t="s">
         <v>34</v>
       </c>
     </row>
@@ -900,21 +903,26 @@
       <c r="A12" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B12" s="9"/>
-      <c r="C12" s="19"/>
-      <c r="D12" s="15"/>
-      <c r="E12" s="9"/>
-    </row>
-    <row r="13" spans="1:5" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B12" s="13"/>
+      <c r="C12" s="15"/>
+      <c r="D12" s="17"/>
+      <c r="E12" s="13"/>
+    </row>
+    <row r="13" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
         <v>35</v>
       </c>
       <c r="B13" s="7">
         <v>6</v>
       </c>
-      <c r="C13" s="10"/>
-      <c r="D13" s="11"/>
-      <c r="E13" s="11"/>
+      <c r="C13" s="18"/>
+      <c r="D13" s="19"/>
+      <c r="E13" s="19"/>
+    </row>
+    <row r="21" spans="8:8" x14ac:dyDescent="0.25">
+      <c r="H21" t="s">
+        <v>36</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="5">
